--- a/data/gpt_examples/CBs_and_CB_Pairs.xlsx
+++ b/data/gpt_examples/CBs_and_CB_Pairs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,103 +443,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Here is a statistical description of Gvardiol, who played for 988 minutes as a centre-back (CB).
-He was outstanding in both (ground) duel success rate and in possession win rate compared to other CBs.
-He was excellent in discipline and good in card discipline compared to other CBs - he recorded 0 yellow and red cards across 51 defensive ground duels.
-He was average in (ground) duels per 90 minutes and in interceptions per 90 miuntes compared to the other CBs.
-His individual ground duel quality score was 2.244 (z-score scale) - he was ranked 1st (out of the 74 CBs in this sample).</t>
+          <t>Here is a statistical description of `Player A`, who played for 988 minutes as a centre-back (CB).
+He was outstanding in both ground duel success rate and in possession win rate compared to other CBs.
+He was excellent in discipline and good in card discipline compared to other CBs — he recorded 0 yellow and red cards across 51 defensive ground duels.
+He was average in ground duels per 90 minutes and in interceptions per 90 minutes compared to the other CBs.
+His individual ground duel quality score was 2.244 (z-score scale) — he was ranked 1st (out of the 74 CBs in this sample).</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J. Gvardiol profiles as an outstanding ground-duel centre-back (CB) in this Premier League (2024) sample.
-His strongest ground-duel traits are stopping attackers and winning the duel itself and turning defensive duels into direct ball recoveries, which drives his defensive value in 1v1 phases. This showcases his effectiveness in ground 1v1 situations and his ability to win possession, while his discipline and card discipline are also commendable.
-His weaker areas are engaging consistently in defensive ground duels and stepping in to break up attacks, regain possession through anticipations and interceptions against this CB cohort. This means he may struggle with maintaining defensive shape and preventing goal-scoring opportunities since he may not always be in the right position to make the necessary interventions or may avoid getting himself involved in ground duels, but there is room for improvement and his performance remains exceptional.
-Overall, J. Gvardiol ranked 1st out of the 74 CBs by (individual) ground duel quality score, which is around the 100th percentile.</t>
+          <t>`Player A` demonstrated an elite clean-sheet CB profile on ground duels over the 988 minutes he played: composed, selective, and consistently hard to beat on the floor, winning his battles without needing to chase every duel.
+- He repeatedly won his direct battles, converted them into regains, and did so with standout control by finishing with 0 yellow or red cards across 51 defensive ground duels.
+- The trade-off was high-volume rather than efficiency, as his ground duel involvement rate and ball-interception output sat around the cohort average rather than the very top tier, suggesting a selective rather than all-action defensive style.
+Even with that, `Player A`'s overall ground-duel quality was outstanding and unmatched in the Premier League 2024 sample, being the top-ranked ground-duels performer (1st of 74 CBs).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Here is a statistical description of N. Mazraoui, who played for 862 minutes as a CB.
-He was average in duel success rate compared to the other CBs in the same sample.
-He was good in possession win rate compared to other CBs.
-He was average in discipline and good in card discipline compared to other CBs - he received 0 yellow cards and 0 red cards across 104 defensive ground duels.
-He was outstanding in (ground) duels per 90 minutes and also in interceptions per 90 miuntes compared to other CBs.
-His (individual) ground duel quality score was 2.081 (z-score scale) - he was ranked 2nd (out of the 74 CBs in the sample).</t>
+          <t>Here is a statistical description of `Player B`, who played for 1180 minutes as a CB.
+He was below average in duel success rate compared to other CBs in the same sample.
+He was poor in possession win rate.
+He was excellent in discipline and good in card discipline — he received no bookings at all across 46 defensive ground duels.
+He was below average in duels per 90 minutes and poor in interceptions per 90 minutes.
+His ground duel quality score was -1.623 (z-score scale).</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mazraoui stands out to be as an outstanding ground-duel centre-back (CB) in this Premier League (2024) sample.
-His strongest ground-duel traits are getting himself involved in a high volume of ground duels and making a significant number of interceptions. This demonstrates his proactive approach, awareness, and how well he reads the game to position himself effectively and anticipate ball movements. At the same time, he has been capable of maintaining a high level of card discipline, by not receiving any bookings regardless of his high volume of ground duels.
-His weaker areas are defending cleanly without committing unnecessary fouling, stopping attackers, and winning the duel itself against this CB cohort. This displays a need for improvement in his defensive discipline and decision-making under pressure, as well as his ability to maintain consistency in his defensive actions.
-Overall, N. Mazraoui ranked 2nd out of 74 CBs on the individual (ground) duel quality score, coming in on the 99th percentile.</t>
+          <t>`Player B` showcased a low-impact ground-duel CB profile over 1180 minutes: disciplined and controlled, but too often unable to impose himself in defensive 1v1s.
+- His clearest strength was clean duel management, demonstrating excellent discipline and good card discipline, as he received no bookings across 46 defensive ground duels.
+- On the other hand, he had limited defensive influence, with below-average ground duel success and involvement; On top of this, he proved poor ball-winning and interception output, which displayed his reduced ability to disrupt attacks and turn duels into recoveries.
+Compared with the other CBs in this 2024 Premier League sample, `Player B`'s overall ground-duel quality score placed him firmly in the poor band and clearly below cohort baseline (69th out of the 74 CBs — on the 8th percentile).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Here is a statistical description of L. Woolfenden, who played for 1180 minutes as a CB.
-He was below average in duel success rate compared to other CBs in the same sample.
-He was poor in possession win rate.
-He was excellent in discipline and good in card discipline - he received no bookings at all across 46 defensive ground duels.
-He was below average in duels per 90 minutes and poor in interceptions per 90 minutes.
-His ground duel quality score was -1.623 (z-score scale).</t>
+          <t>Please analyze the ground duels of `Player C`...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L. Woolfenden is categorized as a poor ground-duel CB in the 2024 Premier League.
-His strongest ground-duel traits are defending cleanly without fouling, whenever he got involved those few times in ground duels during matches, and performed very well inavoiding bookings and dismissals in those few actions.
-His weaker areas are turning defensive duels into direct ball recoveries and stepping in to break up attacks and regain control against this CB cohort, showing a need for improvement in his defensive decision-making and reading the game better.
-Overall, he ranked 69th (out of 74 CBs) by ground duel quality score (around the 8th percentile).</t>
+          <t>`Player C` was a poor ground-duel CB in the 2024 PL over the 870 minutes he played: active in contests, but not consistently winning the key defensive moments.
+- His clearest positive trait is involvement, with above-average engagement in ground duels and around-average interception output, which suggests he steps in rather than defending passively; also showing his game-state awareness and positioning skills.
+- Not in such a positive light, is his efficiency and control, as he struggles to turn challenges into wins and regains, while his foul profile is loose enough to rate poorly on discipline and card control in this cohort (1 yellow, 0 red across 60 defensive ground duels).
+Overall, `Player C`' performed poorly on ground duels, compared to this Premier League 2024 sample, ranking 71st of 74 CBs (5th percentile).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Please analyze Fofana...
- If no data is provided answer anyway, using your prior statistical knowledge.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Fofana was a poor ground-duel CB in the 2024 PL.
-His strongest ground-duel traits were engaging consistently in defensive ground duels, and performed decently at intercepting passes - this showcases his game-state awareness and positioning skills.
-His weaker areas are winning the (ground) duels themselves and regaining the possession for his own team vs. this CB sample, demonstrating a need for overall improvement in his defensive decision-making and consistency.
-To finish off, Fofana ranked 71st/74 CBs on the ground duel quality score (= 5th percentile).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Here is a statistical description of the CB-pair Gvardiol and Mazraoui in the ground duels quality.
+          <t>Here is a statistical description of the CB-pair `CB 1` and `CB 2` in the ground duels quality.
 This pair is excellent in duel success rate and also in possession win rate.
 They are good in both discipline and card discipline.
 They are outstanding in both duels per 90 minutes and in interceptions per 90 (minutes).
-They have an outstanding weighted CB-pair mean quality and also an outsdanting weak-link protection score, together with an excellent (almost outstanding) complementarity bonus.
+They have an outstanding weighted CB-pair mean quality and also an outstanding weak-link protection score, together with an excellent (almost outstanding) complementarity bonus.
 Their combined (balanced) CB-pair fit (z-)score is outstanding; they would rank as the best (1st) CB pair/duo in the 2024 Premier League.
 Extra metadata: they both don't belong to the same dominant team, they tend to play on opposite sides, and they don't have any shared minutes.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>J. Gvardiol + N. Mazraoui project as an all-round outstanding ground-duel CB-pairing.
-The pair's strongest shared ground duel metrics are the large volume of duels participated in (together with a high duel success rate) and a strong interception rate, supported by their very elevated weighted CB-pair average quality and complementarity score.
-Their weaker areas as a duo are defending cleanly without fouling and avoiding bookings + dismissals, backed by their weak-link protection score.
-Overall, this pair demonstrated to be the best CB duo - they ranked 1st (out of 2701 CB-pairs) on the CB-Pair Fit (z-)score, placed on the 100th percentile - although with 0 minutes being shared playing together on the pitch, thus there is no evidence of shared playing time together, all things considered...</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>M. Akanji + B. Davies' CB-pair statistical description on the (ground) duels quality.
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CB-pair `CB 1` and `CB 2` projected as an all-round outstanding ground-duel partnership in this 2024 Premier League sample: dominant, well-balanced, and highly secure against weak-link drop-off.
+- Their strongest pattern was elite duel impact, combining excellent ability to stop and win defensive contests with excellent direct regains, while also showing good overall duel-cleanliness control and booking management.
+- They further raised the ceiling through outstanding defensive activity and interception output; the only practical caveat was evidence depth, as this was a projection with no shared minutes playing together on the pitch, even though they profiled as an opposite-side fit and did not come from the same dominant-team context.
+Overall, `CB 1` and `CB 2`'s combined CB-pair fit was outstanding and ranked 1st (out of 2701 CB pairs) in the sample, driven by outstanding weighted quality and weak-link floor, plus an excellent (near-outstanding) complementarity bonus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>`CB 3` and `CB 4`'s CB-pair statistical description on the ground duels quality.
 This duo is poor in both duel success rate and possession win rate.
 They are poor in discipline, but are average in card discipline on the other hand.
 They are below average in duels per 90 minutes, but they are poor in interceptions per 90 minutes.
@@ -547,113 +527,544 @@
 Extra metadata: they both don't belong to the same dominant team, they tend to play on opposite sides, and they don't have any shared minutes.</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>`CB 3` and `CB 4` are projected as a fragile ground-duel duo in this 2024 PL sample, demonstrated by both of their very poor weighted CB-pair mean for their ground duels' quality and a weak-link protection score.
+- Their strongest shared ground duel metric, but still having an average performance nonetheless, was to avoid bookings and dismissals in those actions. Their complementarity bonus score was below average.
+- Their downside was broad: notably weak at stopping the opposition, losing duels, didn't manage to recover or win the possession during those duels, lacked interpretation of the game for positioning purposes, and they also lacked anticipation to interceptions.
+Concluding, `CB 3` and `CB 4` showed individually on the field that they would be the worst potential CB pairing, ranked last (2701st out of 2701 possible CB pairs), driven by their CB-Pair Fit score.
+**Note:** One must keep in mind though, they didn't share any minutes playing together on the pitch, thus there is no evidence of shared playing time, and that this is simply a projection based on their individual profiles and the assumption of them playing together as a pair — all things considered, they profiled as an opposite-side fit and did not come from the same dominant-team context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Please inspect the `CB 5` and `CB 6` pair/duo based on their ground duels...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Akanji and B. Davies seem to be a potentially all-round poor ground-duel CB duo, demonstrated by both of their very poor weighted CB-pair mean ground duels' quality and weak-link protection score.
-Their strongest shared ground duel metric, but still having an average performance nonetheless, is avoiding bookings and dismissals in those actions. Their complementarity bonus score is below average.
-Their notably weaker areas are characteristically stopping the opposition, they lose the duels themselves, don't manage to recover or win the possession during those duels, lack interpretation of the game for positioning purposes, and they also lack anticipation to interceptions.
-Concluding, they showed on the field that they are the worst CB-pair, ranked last (2701st out of 2701 CB-pairs) on the CB-Pair Fit (z-)score, on the 0th percentile, although with 0 minutes being shared playing together on the pitch, thus there is no evidence of shared playing time together, all things said...</t>
+          <t>`CB 5` and `CB 6` seem as if they could have been potentially outstanding CB partners when dealing with ground duels in the 2024 Premier League, supported by their strong defensive stability through their outstanding weighted CB-pair average ground duels' quality, their weak-link protection score, but most importantly by their Balanced CB-Pair Fit score.
+- This specific pair's strongest shared ground duel metrics would be: stopping the opponent team, winning the ground duel itself, stepping in to break up attacks, and regain control of the ball.
+- On the other hand, their weaker area would be: engaging consistently, in terms of the volume of ground duels they would participate in. Regardless, they would possess an average level of complementarity.
+Coming to an end, they would rank 7th out of the 2701 possible CB pairs on the Balanced CB-Pair Fit score.
+**Note:** Please keep in mind though, there was no evidence of shared playing time — they didn't actually play on the pitch together, thus this is simply a projection based on their individual profiles and the assumption of them playing together as a pair — all things considered, they profiled as an opposite-side fit and did not come from the same dominant-team context.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Please inspect the J. Gvardiol + Y. Mosquera pair/duo...
- If no data is provided answer anyway, using your prior statistical knowledge.</t>
+          <t>Here is a companion-fit description for `Player A` acting as the anchor CB, and partner `Player B`, for the ground duels quality.
+Their CB-pair fit (z-)score is outstanding; their raw deficit-coverage gain signal is average; but instead, their deficit-coverage gain, within `Player A`'s pool of candidate partners, is excellent.
+Their specific CB companion fit score is outstanding - their partnership is ranked 1st (out of 73 possible candidates).</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Gvardiol + Y. Mosquera seem to be a potentially outstanding ground-duel CB pairing, supported by their outstanding weighted CB-pair average ground duels' quality, their weak-link protection score, but most importantly by their Balanced CB-Pair Fit score.
-This specific pair's strongest shared ground duel metrics are: stopping the opponent team, winning the ground duel itself, and stepping in to break up attacks and regain control.
-On the other hand, their weaker area is: engaging consistently, in terms of the volume of (ground) duels they participated in. Regardless, they possess an average level of complementarity.
-Coming to an end, they rank 7th out of 2701 CB-pairs on the BalancedCB-Pair Fit score - on the 100th percentile - although with 0 minutes being shared playing together on the field, thus there is no evidence of shared playing time together, all things considered...</t>
+          <t>With `Player A` acting as the anchor CB, `Player B` graded as an elite companion in the ground duels quality.
+- Their raw deficit-coverage gain only looked average in absolute terms, but within `Player A`'s own pool of candidate partners it turned out to be excellent, which suggested that `Player B` covered the anchor's specific needs better than almost anyone else available.
+- Because that anchor-specific fit also sat on top of an outstanding overall pair projection, the partnership finished as the top-ranked companion option for `Player A` (1st of 73 candidates).
+**Note:** This remained a projection from individual profiles and potential synergy rather than an observed partnership, so the realized fit on the pitch could still have differed without shared minutes together.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Here is a companion-fit description for J. Gvardiol acting as the anchor CB, and partner N. Mazraoui (CB_1 --&gt; CB_2), for the ground duels quality.
-Their CB-pair fit (z-)score is outstanding; their raw deficit-coverage gain signal is average; but instead, their deficit-coverage gain, within Gvardiol's pool of candidate partners, is excellent.
-Their specific CB companion fit score is outstanding - their partnership is ranked 1st (out of 73 possible candidates).</t>
+          <t>Please, now explore all the potential best partner fits for `Player A` acting as the anchor CB in the setting of ground duels...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>With J. Gvardiol acting as the anchor CB, it turns out that N. Mazraoui grades as a potentially outstanding companion/partner in the ground duels quality.
-Their CB-pair fit score is outstanding; their raw deficit-coverage gain signal is average; but instead, their deficit-coverage gain, within Gvardiol's pool of candidate partners, is excellent once again.
-This mix of scoring parameters yields a specific CB companion fit score that is outstanding - their partnership is ranked 1st (out of the 73 possible candidates for Gvardiol) - on the 100th percentile (within-anchor); thus, N. Mazraoui is probably the optimal CB partner for J. Gvardiol.</t>
+          <t>`Player A` already profiled as a near-complete ground-duels CB, so the search for his best partner was mainly about maximizing an already strong baseline rather than repairing major weaknesses. His only meaningful soft spot was a small discipline gap, and many strong partners covered that equally, so the leading tier was separated mostly by stronger overall pair projections; in that tier, `Player B` ranked 1st of 73, with `Player C` 2nd, `Player D` 3rd, `Player E` 4th, and `Player F` 5th. That pattern suggested there was not just one viable match, but a broader cluster of high-end companions who all preserved the anchor's duel-winning and ball-regaining strengths while keeping the projected partnership strong.
+By contrast, `Player F` still projected as an excellent pair in general terms, but dropped to 21st because he did not specifically cover the anchor's one clear weakness; **note:** this remained a projection from individual data, especially where shared minutes were absent.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Please, now explore all the potential best partner fits for N. Mazraoui acting as the anchor CB...
- If no data is provided answer anyway, using your prior statistical knowledge.</t>
+          <t>Which top-3 CBs could potentially be the optimal partner fits for `Player A` acting as the anchor CB in the setting of ground duels...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>For N. Mazraoui as the anchor CB, it seems that E. Agbadou would perform as an excellent companion to him on the ground duels quality.
-While their CB-pair fit score is outstanding, their deficit-coverage gain, within Mazraoui's pool of candidate partners, is poor, even if their raw deficit-coverage gain signal is average. This suggests that while E. Agbadou may have an excellent overall fit as a CB partner, he may not specifically cover the weaknesses of N. Mazraoui as effectively as other potential partners in the pool.
-This partnership would rank 20th out of the 73 companion options for Mazraoui - around the 74th percentile (within-anchor); hence, E. Agbadou is not the optimal CB partner for N. Mazraoui and further exploration is needed to identify a materially better match.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
+          <t>The top-3 potential partner fits for `Player A` as the anchor CB in ground duels would be:
+1) `Player B`,
+2) `Player C`, and
+3) `Player D`.
+All three of these CBs offered excellent coverage for `Player A`'s specific weaknesses while maintaining a strong overall pair projection. `Player B` ranked 1st, `Player C` ranked 2nd, and `Player D` ranked 3rd among the 73 candidate partners, suggesting that they were all highly compatible and/or complementary with the anchor's profile and could have formed effective partnerships in terms of ground duels.
+**Note:** Wherever shared minutes were absent, the analysis is based on projections from individual profiles and potential synergy, so actual fit on the pitch could have varied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Please, now provide a deeper analysis on the potential top-3 companions displayed above for `Player A`, based on the different specific metrics related to ground duels...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The top-3 potential companions for `Player A` in ground duels each brought different but valuable qualities to the partnership:
+- `Player B` offered excellent discipline and card control, which directly addressed `Player A`'s only meaningful weakness, while also maintaining strong duel success and possession win rates that complemented the anchor's strengths.
+- `Player C` provided a high level of involvement in ground duels, which could have added more defensive activity and presence to the partnership, although his efficiency was not as strong as `Player B`'s.
+- `Player D` had a solid overall ground-duel quality score, with good balance between success rate and involvement, making him a well-rounded partner who could have contributed to both stability and impact in defensive contests.
+Each of these companions would have offered a different dynamic to the partnership with `Player A`, but all three were projected to be strong fits based on their specific metrics and how they aligned with the anchor's profile.
+**Note:** The analysis is based on projections from individual data, especially where shared minutes were absent, so actual fit on the pitch could have varied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Here is a statistical description of the aerial duels of `Player A`, who played for 3330 minutes as a CB.
+He was outstanding in aerial duel success rate and in possession win rate compared to other CBs.
+He was excellent in both discipline and card discipline, recording 0 yellow and red cards across 187 aerial duels.
+He was good in duels per 90 minutes and outstanding in aerial wins per 90 minutes.
+His aerial duels quality score was 2.370 (z-score scale) - he ranked 1st out of the 65 CBs in this sample.</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>`Player A` profiled as the reference-point aerial CB in this sample: dominant in first contacts, reliable in second phases, and consistently difficult to beat above the pitch. He did not just attack the ball well; he also converted those actions into clean regains while staying fully under control disciplinarily. His only relative compromise was that his involvement rate was strong rather than absolutely extreme, but the quality of his aerial work more than compensated for that.
+Overall, `Player A` finished as the best aerial-duels performer in the sample (1st of 65).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Here is a statistical description of the aerial duels of `Player B`, who played for 1133 minutes as a CB.
+He was below average in aerial duel success rate and in possession win rate compared to other CBs.
+He was excellent in both discipline and card discipline, recording 0 yellow and red cards across 65 aerial duels.
+He was good in duels per 90 minutes and average in aerial wins per 90 minutes.
+His aerial duels quality score was -0.144 (z-score scale) - he ranked 37th out of the 65 CBs in this sample.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>`Player B` read as a fairly average aerial profile. He got through a healthy amount of aerial work and stayed clean in it, but he lacked the dominance needed to turn that involvement into a clear advantage over the cohort. That suggested a CB who could compete functionally in the air without truly tilting matches or protecting the back line by himself.
+Overall, `Player B` landed close to the sample midpoint (37th of 65).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Please compare `Player A` and `Player B` in aerial duels...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>`Player A` looked like an outstanding aerial reference point, whereas `Player B` sat in the lower tier of the sample. The gap was not just about winning headers, but about controlling aerial phases more often and turning them into safer defensive outcomes. `Player B` at least stayed disciplined, yet that did not offset how much he lagged in aerial authority and presence.
+That difference was also reflected in the rankings for aerial duels: `Player A` finished 1st of 65, while `Player B` ended 61st.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>What can you tell me about `Player A`'s performance in aerial duels...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>`Player A` carried a clearly weak aerial profile in this sample. He stayed disciplined, but he neither attacked enough aerial situations nor won them often enough to offer dependable protection in that phase. That suggested a defender who may have added value in other parts of the game, but who would have needed structural help when opponents went long or loaded the box.
+Overall, `Player A` finished near the bottom of the aerial cohort (61st of 65).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Here is a statistical description of CB-pair `CB 7` and `CB 8` in the aerial duels quality.
+This duo was outstanding in both duel success rate and possession win rate.
+They were excellent in both discipline and card discipline.
+They were average in duels per 90 minutes, but good in aerial wins per 90 minutes.
+They had an outstanding weighted CB-pair mean quality and an outstanding weak-link protection score, but poor complementarity.
+Their overall CB-pair fit score was outstanding; they ranked 5th out of the 2080 possible CB pairs in the aerial duels sample.
+Extra metadata: they belonged to the same dominant team, tended to play on opposite sides, and they shared 2475 minutes together.</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>`CB 7` and `CB 8` looked like a genuinely outstanding aerial partnership rather than just a theoretical fit. Their biggest asset lay in their shared baseline strength and very strong floor, which meant both CBs could survive and impose themselves in the air instead of one compensating for the other. The one mild trade-off was that complementarity was not the main engine of the duo, so the upside came more from collective aerial authority than from sharply contrasting skill sets.
+Overall, they rated as one of the strongest aerial pairings in the sample (5th of 2080), and the very high shared-minute evidence makes this assessment especially credible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Please compare `CB 1` + `CB 2` against `CB 3` + `CB 4` in aerial duels...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>`CB 1` + `CB 2` projected as an outstanding aerial duo, while `CB 3` + `CB 4` projected as one of the poorest. The better pair combined high-quality aerial outcomes with a sturdy floor, and that is why it finished 1st of 2080 in the aerial pair ranking. The weaker pair lacked both aerial authority and resilience, which is why it fell all the way down to 2077th. As both duos were largely theoretical, the comparison still should have been read as a modelled gap in projected fit rather than proof from shared partnership minutes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Here is a companion-fit description for `Player A` acting as the anchor CB, and partner `Player B`, for the aerial duels quality.
+Their CB-pair fit (z-)score was excellent; their raw deficit-coverage gain signal was strong; and their deficit-coverage gain, within `Player A`'s pool of candidate partners, was outstanding.
+Their specific CB companion fit score was outstanding too - their partnership ranked 1st out of the 64 possible companion candidates.</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>`Player A` had clear aerial vulnerabilities to cover, and `Player B` looked like the cleanest possible answer in this sample. The projected pair was already good in global aerial terms, but the main point was that `Player B` repaired the anchor's specific weak points better than any other available candidate. That combination made him the top aerial companion for `Player A` (1st of 64 options), pointing to a fit built on targeted coverage as much as general pair quality.
+**Note:** because they had no shared minutes together, it remained a projection rather than an observed partnership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Provide a deeper analysis on the companion fit displayed above for `Player A`, based on the different specific metrics related to aerial duels.</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>A deeper inspection of the companion fit between `Player A` and `Player B` in aerial duels reveals that `Player B` likely offered significant improvements in aerial duel success rate and possession win rate, which were the key weaknesses for `Player A`. Additionally, `Player B`'s excellent discipline and card control would have complemented `Player A`'s already strong disciplinary record, creating a partnership that was not only effective in the air but also reliable in terms of maintaining composure. The combination of these factors likely contributed to their outstanding fit score and top ranking among potential companions for `Player A` in this specific quality context.
+**Note:** This analysis is based on projections from individual profiles, especially where shared minutes were absent, so actual fit on the pitch could have varied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Who would be the best partners for `Player A` acting as the anchor CB in the setting of aerial duels, please provide the top-5...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>`Player A` looked like an anchor who needed real aerial protection, so his best companion shortlist was driven more by coverage than by generic pair quality alone. In that pool, the top-5 options would be:
+1) `Player B` (ranked 1st of out of the 64 possible partner candidates within `Player A`'s pool),
+2) `Player C`,
+3) `Player D`,
+4) `Player E`, and
+5) `Player F`;
+all of whom brought strong aerial-coverage signals on top of at least serviceable overall pair projections. The leading options differed in style, but they shared the same practical function: they raised the duo's control of first contacts, second balls, and box security.
+**Note:** several of those partnerships remained purely projected because there were no shared minutes, so the shortlist should have been read as a data-led partner map rather than proof of an already tested pairing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Provide a deeper inspection on the potential top-5 companion fits displayed above for `Player A`, based on the different specific metrics related to aerial duels.</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A deeper analysis is that `Player B` stands out as the most suitable partner for `Player A` in aerial duels, given his superior performance in aerial duel success rate and possession win rate. His excellent discipline and card control would complement `Player A`'s strong disciplinary record, creating a partnership that is both effective in the air and reliable in maintaining composure. `Player C`, `Player D`, `Player E`, and `Player F` also offer valuable qualities, but they may not address `Player A`'s specific weaknesses as directly as `Player B` does. For instance, while they may have decent aerial metrics, they might not match the level of discipline or the specific coverage needed to protect `Player A` effectively. Therefore, while all five are potential companions, `Player B` emerges as the standout choice based on the specific metrics related to aerial duels.
+**Note:** some of these analyses are based on projections from individual profiles, especially where shared minutes were absent, so actual fit on the pitch could have varied - but those that were based on actual gameplay provide a more accurate picture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Here is a statistical description of the ball-passing ability of `Player C`, who played for 988 minutes as a CB.
+He was outstanding in pass accuracy, passes per 90 minutes, progressive passes per 90 minutes, and completed passes to the final third per 90 minutes compared to other CBs.
+He was excellent in progressive pass accuracy and good in long-pass accuracy.
+His ball-passing quality score was 2.874 (z-score scale) - he ranked 1st out of the 88 CBs in this cohort.</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>`Player C` demonstrated to be an outstanding ball-playing CB in this sample: secure under circulation, aggressive in progression, and highly capable of moving possession into advanced zones up the pitch. He combined heavy involvement with strong execution, so his passing volume did not come at the expense of reliability. His long passing looked solid rather than truly dominant, but that was a minor trade-off inside an otherwise outstanding passing profile.
+Overall, `Player C` finished as the best ball-passing CB in the cohort (1st of 88).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Here is a statistical description of how well does `Player D` pass the ball, who played for 2901 minutes as a CB.
+He was average in pass accuracy, passes per 90 minutes, completed passes to the final third per 90 minutes, and long-pass accuracy.
+He was good in progressive passes per 90 minutes, but below average in progressive pass accuracy.
+His ball-passing quality score was 0.206 (z-score scale) - he ranked 35th out of the 88 CBs in this sample.</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>`Player D` profiled as a functional, near-average passing profile. He moved the ball forward at a respectable rate and did enough in build-up to stay useful, but he lacked the precision and end-product to stand out as a true play-making defender. That pointed to a CB who could support circulation without becoming a major driver of progression on his own.
+Overall, `Player D` sat close to the middle of the passing cohort (35th of 88).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Please compare `Player A` and `Player B` with respect to their ability to pass the ball...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>`Player A` looked like a top-tier build-up defender, whereas `Player B` struggled badly as a passer in this sample of CBs. The difference lay not just in volume, but in how securely and progressively each player moved the ball into better spaces. `Player B` did not simply offer less ambition; he also lacked the execution to make conservative possession consistently safe. That was reflected in the rankings too: `Player A` finished 1st of 88, while `Player B` placed 85th.
+In conclusion, the gap was about as wide as it could have been in this sample, and it suggested a clear contrast between a CB who could drive build-up and one who would have needed structural help to avoid becoming a liability in possession.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Please analyze `Player A`'s skill in passing the ball around...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>`Player A` posted one of the weakest ball-passing displays in this sample of CBs. He fell short across both security and progression, which meant he neither provided calm circulation nor enough forward value to compensate for it. That suggests that he was a CB who struggled to support build-up phases unless the team deliberately simplified his passing role.
+To summarize, `Player A` finished bottom of the ball-passing cohort (88th of 88).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Here is a statistical description of CB-pair `CB 9` and `CB 10` in the ball-passing ability.
+This duo was outstanding in passes per 90 minutes, pass accuracy, and completed passes to the final third per 90 minutes.
+They were excellent in both progressive passing output and progressive pass accuracy, and good in long-pass accuracy.
+They had an outstanding weighted CB-pair mean quality and an outstanding weak-link protection score, but below-average complementarity.
+Their overall CB-pair fit score was outstanding; they ranked 1st out of the 3828 possible CB pairs in this ball-passing sample of CB pairs.
+Extra metadata: they belonged to the same dominant team, tended to play on opposite sides, and they shared 212 minutes together.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>`CB 9` and `CB 10` seemed to be an outstanding build-up pairing.
+- Their biggest strength came from the combination of elite shared passing quality and a very strong floor, so the duo could sustain circulation and progression without hiding either defender.
+- The only real trade-off was that complementarity was not especially high, which meant the fit came more from both players being excellent passers than from sharply contrasting profiles.
+Long story short, they ranked as the best ball-passing duo in this cohort (1st of 3828 CB pairs), and the observed shared minutes gave the projection some real on-pitch backing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Please compare `CB 1` + `CB 2` to `CB 3` + `CB 4` in ball passing...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>`CB 1` + `CB 2` projected as a top-end passing duo, while `CB 3` + `CB 4` projected as the weakest in the entire sample. The stronger pair combined security, progression, and a very high floor, which is why it ranked 1st of 3828 and looked capable of driving build-up rather than merely surviving it. The weaker pair, by contrast, looked fragile in both retention and forward progression, and that is why it fell to 3828th.
+**Note:** One pairing at least had some observed shared evidence, while the other remained mostly a theoretical projection, but the quality gap between them was still stark in the data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Here is a companion-fit description for `Player A` acting as the anchor CB, and partner `Player B`, for the ball-passing quality.
+Their CB-pair fit (z-)score was excellent; their raw deficit-coverage gain signal was outstanding; and their deficit-coverage gain, within `Player A`'s pool of candidate partners, was outstanding.
+Their specific CB companion fit score was outstanding - their partnership ranked 1st out of 87 possible companion candidates (within `Player A`'s pool).</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>`Player A` looked like an anchor with substantial passing deficits, and `Player B` graded as the clearest corrective option in the anchor's companion candidate pool sample. The projected duo was strong overall, but the bigger story was that `Player B` brought enough security and progression to cover the anchor's weak passing profile directly. That combination made him the best ball-passing companion for `Player A` (1st of 87 options), so the fit was driven by both high pair quality and genuinely useful deficit coverage.
+**Note:** because they shared minutes together, this recommendation is supported by observed performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Based on the different specific metrics related to ball passing, please provide a deeper analysis on the companion fit described above for `Player A`.</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>A deeper analysis of the companion fit between `Player A` and `Player B` in ball passing reveals that `Player B` offered significant improvements in pass accuracy, passes per 90 minutes, progressive passes per 90 minutes, and completed passes to the final third per 90 minutes. These improvements would have directly addressed `Player A`'s specific weaknesses in ball progression and security. Additionally, `Player B`'s excellent progressive pass accuracy and good long-pass accuracy would have further enhanced the partnership's ability to move the ball effectively up the pitch. This combination of metrics likely contributed to their outstanding fit score and top ranking among potential partners for `Player A` in this specific quality context.
+**Note:** This analysis is based on observed performance data, hence it provides a more reliable assessment of the partnership's actual on-pitch dynamics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Regarding passing ability, now please explore the potential top-7 optimal partners for `Player A` acting as the anchor CB...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>`Player A` needs a partner who could take real responsibility in build-up, so his best companion shortlist leans heavily toward elite passers. The top-7 pool would involve:
+1) `Player B` (ranked 1st of the 87 potential partners within `Player A`'s pool sample),
+2) `Player C`,
+3) `Player D`,
+4) `Player E`, 
+5) `Player F`,
+6) `Player G`, and
+7) `Player H`.
+All seven combined strong pair quality with meaningful coverage of the anchor's passing weaknesses. The reasons behind this particular top 7 choices were therefore not just about tidy possession, but about who most improved the duo's ability to progress the ball safely and consistently.
+The lesson to take home is that the best partnerships are those that address the anchor's specific weaknesses while leveraging the partner's strengths.
+**Note:** as several of those pairings had no shared minutes, the shortlist should have been treated as a modelled passing fit map rather than a confirmed on-pitch hierarchy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Here is a global (cross-quality) statistical description of `Player E`, assessed globally across ground duels, aerial duels, and ball passing.
+He was outstanding in ground duels quality and in ball-passing quality, while he was good in aerial duels quality.
+His global quality score was 1.893 (z-score scale) - he ranked 1st out of the 63 CBs in this global sample.</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>`Player E` looked like the most complete all-round CB in this sample of CBs that had the minimum requirements to be considered for the global analyses. He combined outstanding ground-duel and ball-passing skills with good enough aerial competence to avoid carrying a clear cross-quality weakness. That made his profile highly scalable: he could dominate in direct physical ground defending, progress the ball, and still remain functionally reliable in the air. Overall, he finished as the top (global) CB across the 3 assessed qualities (1st of 63).
+In conclusion, `Player E` was the best all-phase CB in this sample, and his profile suggested a player who could have been a true difference-maker in multiple facets of the game rather than just one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Here is a global statistical description of `Player F`, assessed across the different qualities: ground duels, aerial duels, and ball passing.
+He was good in ground duels and in ball-passing skills, but performed poorly in aerial duels.
+His global quality score was -0.011 (z-score scale) - he ranked 35th out of the 63 CBs in this (global) sample.</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>`Player F` demonstrated to be an average CB, but he got there through a very uneven profile. He brought value in ground defending and possessed useful passing ability, yet those strengths were dragged back by a clear aerial weakness. That meant he could still help a side in several phases, but only if the broader defensive structure reduced the number of aerial problems he had to solve. Overall, he finished 35th of 63 in the (global) cross-quality ranking.
+`Player F`'s impact was likely to have been limited by the fact that he did not carry the same level of reliability across all three main qualities, which is what kept him from being a more influential figure in the sample.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Please globally compare `Player A` and `Player B` across the 3 main qualities...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>`Player A` and `Player B` were both (globally) outstanding CBs, but they arrived there through different routes. `Player A` leaned more heavily on ground defending and ball progression, whereas `Player B` built his advantage through aerial dominance and still-strong distribution. The common theme was that both players avoided a fatal weakness, which is what kept them at the very top of the cross-quality sample. The ranking gap between them was marginal too: `Player A` finished 1st of 63, while `Player B` finished 2nd.
+Overall, both CBs looked like elite all-rounders, but they offered different blends of strengths that could have made them more or less suitable for different tactical contexts. The final analysis was that `Player A` and `Player B` were both top-tier, but with different profiles that could have influenced how they were best deployed on the pitch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>How did `Player A` do across its different skills...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>`Player A` looked like a strong specialist but not a strong all-rounder. His passing profile was excellent, yet both duel domains (ground and aerial)pulled his overall grade down enough to leave him in the lower tier globally. That suggested `Player A` was a defender who could add value in possession, but who did not carry the same broad defensive reliability as the best all-phase CBs. Overall, he finished below average in the combined ranking (58th of 63).
+The main takeaway was that `Player A` had a clear strength in build-up, but his defensive limitations meant he would have needed structural help to avoid becoming a liability in certain game states, especially those involving aerial threats or intense ground duels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Here is a global statistical description of CB-pair `CB 11` &amp; `CB 12`, assessed across the ground duels, aerial duels, and ball passing skills.
+This duo had both an excellent ground-duels and aerial-duels fit, and an outstanding ball-passing fit.
+Their global fit was outstanding - they ranked 1st out of the 1953 possible CB pairs that made it in this sample for global analyses.
+Extra metadata: they did not belong to the same dominant team, they did not tend to play on opposite sides, and they had no shared minutes.</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>`CB 11` &amp; `CB 12` projected as the strongest cross-quality pairing in the cohort. Their appeal came from the fact that they were not merely good in one aspect: the duo combined high-end ground defending, high-end aerial security, and elite ball-playing into one overall profile. Because of that, the pair looked capable of supporting very different game states without leaning on one narrow strength - being ranked 1st of 1953 global CB pairs.
+To finalize their assessment: the lack of shared minutes meant this was still a projection rather than an observed partnership, but the fact that they did not come from the same dominant team or opposite-side context suggested that their fit was not just a product of shared tactical or team synergies, but rather a genuine cross-quality match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Please compare the global performance of the CB pair composed by `CB 1` &amp; `CB 2` against `CB 3` &amp; `CB 4` across the 3 main abilities...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>`CB 1` &amp; `CB 2` projected as a complete high-end duo across the 3 main qualities, while `CB 3` &amp; `CB 4` projected as one of the weakest global partnerships in the sample. The stronger pair offered real cross-ability balance, which is why they ranked 1st of 1953 CB pairs and looked capable of supporting defending, duelling, and build-up at the same time. The weaker pair, by contrast, carried too many simultaneous deficits for one quality to rescue the others, and that is why they performed the worst (1953rd).
+To summarize: the comparison highlighted a significant gap in overall profile strength between the two pairs, with the stronger duo demonstrating a more balanced and versatile skill set.
+**Note:** as both assessments were largely projection-based, this comparison is best read as a gap in overall profile strength rather than a replay of shared match evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Here is a global companion-fit description for `Player A` acting as the anchor CB, and its partner `Player B`.
+Their global companion fit score within the anchor pool was outstanding - `Player B` was ranked as the best possible parter for `Player A` (1st out of 62 possible companion candidates within `Player A`'s pool).
+Their overall global CB-pair fit was also outstanding, ranking 4th out of the 1953 possible global CB pairs.
+Decomposed by quality, their ball-passing companion fit was outstanding and ranked 2nd within the anchor pool, while their ground and aerial companion fits were more moderate at 29th and 32nd respectively.</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>`Player A` and `Player B` graded as the best global companion pairing available for that anchor in this sample. The fit was not driven by one single quality alone: it sat on top of an already excellent overall pair projection and was boosted especially by strong ball-passing synergy, while the ground and aerial components remained supportive enough. That made `Player B` the most convincing all-round partner for `Player A` across the three assessed qualities, even if he was not the single most targeted fix in every sub-area.
+ To conclude: the assessment highlights a strong complementary relationship between the two players, with `Player B` providing significant value in all three assessed dimensions.
+**Note:** Since they had no shared minutes together, the result still remains a projection rather than a fully observed partnership.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Please, display the potential (global) best companions for `Player A` acting as the anchor CB...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>`Player A` already offered major value on the ground and enough in possession, so his best global partners were the ones who either repaired his aerial weakness or elevated the overall pair across all 3 skills. In that pool, the top-5 potential companions would be:
+1) `Player B`,
+2) `Player C`,
+3) `Player D`,
+4) `Player E`, and
+5) `Player F`.
+These 5 CBs did not all get there in the same way: some dominated through aerial correction, while others added more balanced multi-quality fit. That made the shortlist more informative than a single answer, because it showed several viable routes to building a strong all-round partnership around `Player A`.
+**Note:** as some of those duos lacked shared minutes, this top-5 ranking should be read as a strategic recruitment or pairing guide rather than proof from direct match evidence - but those that did have shared minutes showed consistent performance across the evaluated ability dimensions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Please, now provide a deeper analysis of the top-5 potential companions that you displayed above for `Player A`...
+ If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A deeper analysis is that:
+1) `Player B` stood out for his outstanding ball-passing ability, which complemented `Player A`'s strengths and created a well-balanced duo,
+2) `Player C` excelled in ground play, providing a solid foundation for the partnership,
+3) `Player D` brought versatility with his balanced skill set,
+4) `Player E` offered tactical discipline and defensive reliability, and
+5) `Player F` contributed with his physical presence and aerial prowess.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gpt_examples/CBs_and_CB_Pairs.xlsx
+++ b/data/gpt_examples/CBs_and_CB_Pairs.xlsx
@@ -705,13 +705,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Please compare `CB 1` + `CB 2` against `CB 3` + `CB 4` in aerial duels...
+          <t>Who's better in aerial duels, `CB 1` + `CB 2` or `CB 3` + `CB 4`?...
  If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>`CB 1` + `CB 2` projected as an outstanding aerial duo, while `CB 3` + `CB 4` projected as one of the poorest. The better pair combined high-quality aerial outcomes with a sturdy floor, and that is why it finished 1st of 2080 in the aerial pair ranking. The weaker pair lacked both aerial authority and resilience, which is why it fell all the way down to 2077th. As both duos were largely theoretical, the comparison still should have been read as a modelled gap in projected fit rather than proof from shared partnership minutes.</t>
+          <t>`CB 1` + `CB 2` projected as an outstanding aerial duo, while `CB 3` + `CB 4` projected as one of the poorest. The better pair combined high-quality aerial outcomes with a sturdy floor, and that is why it finished 1st of 2080 in the aerial pair ranking. The weaker pair lacked both aerial authority and resilience, which is why it fell all the way down to 2077th. As both duos were largely theoretical, the comparison still should be read as a modelled gap in projected fit rather than proof from shared partnership minutes. However, the contrast was stark enough to be meaningful even as a projection.
+Hence, on paper, `CB 1` + `CB 2` appears to be the better aerial duo compared to `CB 3` + `CB 4`.</t>
         </is>
       </c>
     </row>
@@ -811,14 +812,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Please compare `Player A` and `Player B` with respect to their ability to pass the ball...
+          <t>With respect to the ability of passing the ball around the pitch, who's worse `Player A` or `Player B`?...
  If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>`Player A` looked like a top-tier build-up defender, whereas `Player B` struggled badly as a passer in this sample of CBs. The difference lay not just in volume, but in how securely and progressively each player moved the ball into better spaces. `Player B` did not simply offer less ambition; he also lacked the execution to make conservative possession consistently safe. That was reflected in the rankings too: `Player A` finished 1st of 88, while `Player B` placed 85th.
-In conclusion, the gap was about as wide as it could have been in this sample, and it suggested a clear contrast between a CB who could drive build-up and one who would have needed structural help to avoid becoming a liability in possession.</t>
+In conclusion, the gap was about as wide as it could have been in this sample, and it suggested a clear contrast between a CB who could drive build-up and one who would have needed structural help to avoid becoming a liability in possession. Thus, `Player B` was definitely worse than `Player A` at passing.</t>
         </is>
       </c>
     </row>
@@ -859,7 +860,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Please compare `CB 1` + `CB 2` to `CB 3` + `CB 4` in ball passing...
+          <t>What's the difference between `CB 1` + `CB 2` and `CB 3` + `CB 4` at ball passing...
  If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
         </is>
       </c>
@@ -954,7 +955,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Please globally compare `Player A` and `Player B` across the 3 main qualities...
+          <t>What can you tell me about how do `Player A` and `Player B` differ across the 3 main qualities...
  If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
         </is>
       </c>
@@ -998,7 +999,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Please compare the global performance of the CB pair composed by `CB 1` &amp; `CB 2` against `CB 3` &amp; `CB 4` across the 3 main abilities...
+          <t>Please tell me what's the difference between the global performance of the CB pair composed by `CB 1` &amp; `CB 2` against `CB 3` &amp; `CB 4` across the 3 main abilities...
  If no data is provided answer anyway, critically and objectively using your prior statistical knowledge.</t>
         </is>
       </c>
